--- a/工作一对比结果/cnn-dir0.1baseline.xlsx
+++ b/工作一对比结果/cnn-dir0.1baseline.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,6 +622,42 @@
       </c>
       <c r="J5" t="n">
         <v>86.31</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>nonIID(0.1)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>FedAGSA</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>55</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="E6" t="n">
+        <v>144</v>
+      </c>
+      <c r="F6" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="G6" t="n">
+        <v>338</v>
+      </c>
+      <c r="H6" t="n">
+        <v>38.22</v>
+      </c>
+      <c r="I6" t="n">
+        <v>56.69</v>
+      </c>
+      <c r="J6" t="n">
+        <v>86.58</v>
       </c>
     </row>
   </sheetData>
